--- a/artfynd/A 2975-2022 artfynd.xlsx
+++ b/artfynd/A 2975-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113703081</v>
+        <v>113702950</v>
       </c>
       <c r="B2" t="n">
-        <v>8432</v>
+        <v>96082</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>2604</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316525</v>
+        <v>316552</v>
       </c>
       <c r="R2" t="n">
-        <v>6513817</v>
+        <v>6513787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702950</v>
+        <v>113702963</v>
       </c>
       <c r="B3" t="n">
-        <v>96082</v>
+        <v>94192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2604</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316552</v>
+        <v>316566</v>
       </c>
       <c r="R3" t="n">
-        <v>6513787</v>
+        <v>6513794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702963</v>
+        <v>113702964</v>
       </c>
       <c r="B4" t="n">
         <v>94192</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316566</v>
+        <v>316614</v>
       </c>
       <c r="R4" t="n">
-        <v>6513794</v>
+        <v>6513846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113702964</v>
+        <v>113703081</v>
       </c>
       <c r="B5" t="n">
-        <v>94192</v>
+        <v>8432</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>316614</v>
+        <v>316525</v>
       </c>
       <c r="R5" t="n">
-        <v>6513846</v>
+        <v>6513817</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702691</v>
+        <v>113702692</v>
       </c>
       <c r="B6" t="n">
         <v>56826</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>316490</v>
+        <v>316703</v>
       </c>
       <c r="R6" t="n">
-        <v>6513774</v>
+        <v>6513729</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113702790</v>
+        <v>113702691</v>
       </c>
       <c r="B7" t="n">
-        <v>96364</v>
+        <v>56826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,41 +1221,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316760</v>
+        <v>316490</v>
       </c>
       <c r="R7" t="n">
-        <v>6513582</v>
+        <v>6513774</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113702692</v>
+        <v>113702790</v>
       </c>
       <c r="B8" t="n">
-        <v>56826</v>
+        <v>96364</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,45 +1331,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316703</v>
+        <v>316760</v>
       </c>
       <c r="R8" t="n">
-        <v>6513729</v>
+        <v>6513582</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 2975-2022 artfynd.xlsx
+++ b/artfynd/A 2975-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702950</v>
+        <v>113702691</v>
       </c>
       <c r="B2" t="n">
-        <v>96082</v>
+        <v>56826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2604</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316552</v>
+        <v>316490</v>
       </c>
       <c r="R2" t="n">
-        <v>6513787</v>
+        <v>6513774</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702963</v>
+        <v>113702964</v>
       </c>
       <c r="B3" t="n">
-        <v>94192</v>
+        <v>94196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316566</v>
+        <v>316614</v>
       </c>
       <c r="R3" t="n">
-        <v>6513794</v>
+        <v>6513846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702964</v>
+        <v>113702950</v>
       </c>
       <c r="B4" t="n">
-        <v>94192</v>
+        <v>96086</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316614</v>
+        <v>316552</v>
       </c>
       <c r="R4" t="n">
-        <v>6513846</v>
+        <v>6513787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703081</v>
+        <v>113702692</v>
       </c>
       <c r="B5" t="n">
-        <v>8432</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,41 +1009,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>316525</v>
+        <v>316703</v>
       </c>
       <c r="R5" t="n">
-        <v>6513817</v>
+        <v>6513729</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702692</v>
+        <v>113702963</v>
       </c>
       <c r="B6" t="n">
-        <v>56826</v>
+        <v>94196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,45 +1119,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>316703</v>
+        <v>316566</v>
       </c>
       <c r="R6" t="n">
-        <v>6513729</v>
+        <v>6513794</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113702691</v>
+        <v>113703081</v>
       </c>
       <c r="B7" t="n">
-        <v>56826</v>
+        <v>8432</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,45 +1225,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316490</v>
+        <v>316525</v>
       </c>
       <c r="R7" t="n">
-        <v>6513774</v>
+        <v>6513817</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>113702790</v>
       </c>
       <c r="B8" t="n">
-        <v>96364</v>
+        <v>96368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 2975-2022 artfynd.xlsx
+++ b/artfynd/A 2975-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702691</v>
+        <v>113702964</v>
       </c>
       <c r="B2" t="n">
-        <v>56826</v>
+        <v>94196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316490</v>
+        <v>316614</v>
       </c>
       <c r="R2" t="n">
-        <v>6513774</v>
+        <v>6513846</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702964</v>
+        <v>113702950</v>
       </c>
       <c r="B3" t="n">
-        <v>94196</v>
+        <v>96086</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>2604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316614</v>
+        <v>316552</v>
       </c>
       <c r="R3" t="n">
-        <v>6513846</v>
+        <v>6513787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702950</v>
+        <v>113702963</v>
       </c>
       <c r="B4" t="n">
-        <v>96086</v>
+        <v>94196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2604</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316552</v>
+        <v>316566</v>
       </c>
       <c r="R4" t="n">
-        <v>6513787</v>
+        <v>6513794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1107,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702963</v>
+        <v>113702790</v>
       </c>
       <c r="B6" t="n">
-        <v>94196</v>
+        <v>96368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>316566</v>
+        <v>316760</v>
       </c>
       <c r="R6" t="n">
-        <v>6513794</v>
+        <v>6513582</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1319,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113702790</v>
+        <v>113702691</v>
       </c>
       <c r="B8" t="n">
-        <v>96368</v>
+        <v>56826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,41 +1327,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316760</v>
+        <v>316490</v>
       </c>
       <c r="R8" t="n">
-        <v>6513582</v>
+        <v>6513774</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 2975-2022 artfynd.xlsx
+++ b/artfynd/A 2975-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702964</v>
+        <v>113702790</v>
       </c>
       <c r="B2" t="n">
-        <v>94196</v>
+        <v>96368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316614</v>
+        <v>316760</v>
       </c>
       <c r="R2" t="n">
-        <v>6513846</v>
+        <v>6513582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702950</v>
+        <v>113702692</v>
       </c>
       <c r="B3" t="n">
-        <v>96086</v>
+        <v>56826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,41 +793,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2604</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316552</v>
+        <v>316703</v>
       </c>
       <c r="R3" t="n">
-        <v>6513787</v>
+        <v>6513729</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702963</v>
+        <v>113703081</v>
       </c>
       <c r="B4" t="n">
-        <v>94196</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316566</v>
+        <v>316525</v>
       </c>
       <c r="R4" t="n">
-        <v>6513794</v>
+        <v>6513817</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113702692</v>
+        <v>113702950</v>
       </c>
       <c r="B5" t="n">
-        <v>56826</v>
+        <v>96086</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,45 +1009,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2604</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>316703</v>
+        <v>316552</v>
       </c>
       <c r="R5" t="n">
-        <v>6513729</v>
+        <v>6513787</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702790</v>
+        <v>113702964</v>
       </c>
       <c r="B6" t="n">
-        <v>96368</v>
+        <v>94196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>316760</v>
+        <v>316614</v>
       </c>
       <c r="R6" t="n">
-        <v>6513582</v>
+        <v>6513846</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703081</v>
+        <v>113702691</v>
       </c>
       <c r="B7" t="n">
-        <v>8432</v>
+        <v>56826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,41 +1221,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316525</v>
+        <v>316490</v>
       </c>
       <c r="R7" t="n">
-        <v>6513817</v>
+        <v>6513774</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113702691</v>
+        <v>113702963</v>
       </c>
       <c r="B8" t="n">
-        <v>56826</v>
+        <v>94196</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,45 +1331,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316490</v>
+        <v>316566</v>
       </c>
       <c r="R8" t="n">
-        <v>6513774</v>
+        <v>6513794</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 2975-2022 artfynd.xlsx
+++ b/artfynd/A 2975-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702790</v>
+        <v>113702692</v>
       </c>
       <c r="B2" t="n">
-        <v>96368</v>
+        <v>56826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316760</v>
+        <v>316703</v>
       </c>
       <c r="R2" t="n">
-        <v>6513582</v>
+        <v>6513729</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702692</v>
+        <v>113702963</v>
       </c>
       <c r="B3" t="n">
-        <v>56826</v>
+        <v>94196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,45 +797,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316703</v>
+        <v>316566</v>
       </c>
       <c r="R3" t="n">
-        <v>6513729</v>
+        <v>6513794</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703081</v>
+        <v>113702950</v>
       </c>
       <c r="B4" t="n">
-        <v>8432</v>
+        <v>96086</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316525</v>
+        <v>316552</v>
       </c>
       <c r="R4" t="n">
-        <v>6513817</v>
+        <v>6513787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113702950</v>
+        <v>113702790</v>
       </c>
       <c r="B5" t="n">
-        <v>96086</v>
+        <v>96368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2604</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>316552</v>
+        <v>316760</v>
       </c>
       <c r="R5" t="n">
-        <v>6513787</v>
+        <v>6513582</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113702691</v>
+        <v>113703081</v>
       </c>
       <c r="B7" t="n">
-        <v>56826</v>
+        <v>8432</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,45 +1221,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316490</v>
+        <v>316525</v>
       </c>
       <c r="R7" t="n">
-        <v>6513774</v>
+        <v>6513817</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113702963</v>
+        <v>113702691</v>
       </c>
       <c r="B8" t="n">
-        <v>94196</v>
+        <v>56826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,41 +1327,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316566</v>
+        <v>316490</v>
       </c>
       <c r="R8" t="n">
-        <v>6513794</v>
+        <v>6513774</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 2975-2022 artfynd.xlsx
+++ b/artfynd/A 2975-2022 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702964</v>
+        <v>113703081</v>
       </c>
       <c r="B6" t="n">
-        <v>94196</v>
+        <v>8432</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>316614</v>
+        <v>316525</v>
       </c>
       <c r="R6" t="n">
-        <v>6513846</v>
+        <v>6513817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703081</v>
+        <v>113702964</v>
       </c>
       <c r="B7" t="n">
-        <v>8432</v>
+        <v>94196</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316525</v>
+        <v>316614</v>
       </c>
       <c r="R7" t="n">
-        <v>6513817</v>
+        <v>6513846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 2975-2022 artfynd.xlsx
+++ b/artfynd/A 2975-2022 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702963</v>
+        <v>113702950</v>
       </c>
       <c r="B3" t="n">
-        <v>94196</v>
+        <v>96086</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>2604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316566</v>
+        <v>316552</v>
       </c>
       <c r="R3" t="n">
-        <v>6513794</v>
+        <v>6513787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702950</v>
+        <v>113702964</v>
       </c>
       <c r="B4" t="n">
-        <v>96086</v>
+        <v>94196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2604</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316552</v>
+        <v>316614</v>
       </c>
       <c r="R4" t="n">
-        <v>6513787</v>
+        <v>6513846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113702790</v>
+        <v>113702691</v>
       </c>
       <c r="B5" t="n">
-        <v>96368</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,41 +1009,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>316760</v>
+        <v>316490</v>
       </c>
       <c r="R5" t="n">
-        <v>6513582</v>
+        <v>6513774</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703081</v>
+        <v>113702963</v>
       </c>
       <c r="B6" t="n">
-        <v>8432</v>
+        <v>94196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>316525</v>
+        <v>316566</v>
       </c>
       <c r="R6" t="n">
-        <v>6513817</v>
+        <v>6513794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113702964</v>
+        <v>113703081</v>
       </c>
       <c r="B7" t="n">
-        <v>94196</v>
+        <v>8432</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316614</v>
+        <v>316525</v>
       </c>
       <c r="R7" t="n">
-        <v>6513846</v>
+        <v>6513817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113702691</v>
+        <v>113702790</v>
       </c>
       <c r="B8" t="n">
-        <v>56826</v>
+        <v>96368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,45 +1331,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316490</v>
+        <v>316760</v>
       </c>
       <c r="R8" t="n">
-        <v>6513774</v>
+        <v>6513582</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 2975-2022 artfynd.xlsx
+++ b/artfynd/A 2975-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2975-2022 artfynd.xlsx
+++ b/artfynd/A 2975-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>113702963</v>
       </c>
       <c r="B2" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702950</v>
+        <v>113702964</v>
       </c>
       <c r="B3" t="n">
-        <v>96331</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2604</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316553</v>
+        <v>316614</v>
       </c>
       <c r="R3" t="n">
-        <v>6513787</v>
+        <v>6513846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,57 +877,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702692</v>
+        <v>113702950</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316703</v>
+        <v>316553</v>
       </c>
       <c r="R4" t="n">
-        <v>6513729</v>
+        <v>6513787</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,16 +981,11 @@
         <v>113702691</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1107,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702964</v>
+        <v>113702692</v>
       </c>
       <c r="B6" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,37 +1094,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>316614</v>
+        <v>316703</v>
       </c>
       <c r="R6" t="n">
-        <v>6513846</v>
+        <v>6513729</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,12 +1191,7 @@
         <v>113703081</v>
       </c>
       <c r="B7" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,15 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113702790</v>
+        <v>113702769</v>
       </c>
       <c r="B8" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,16 +1300,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1359,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316760</v>
+        <v>316697</v>
       </c>
       <c r="R8" t="n">
-        <v>6513582</v>
+        <v>6513833</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,6 +1383,107 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113702790</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Medbön, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>316760</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6513582</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 2975-2022 artfynd.xlsx
+++ b/artfynd/A 2975-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702963</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702964</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702950</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702691</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702692</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703081</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702769</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,8 +1528,23 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702790</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>